--- a/artfynd/A 23496-2023 artfynd.xlsx
+++ b/artfynd/A 23496-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23496-2023 artfynd.xlsx
+++ b/artfynd/A 23496-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99308322</v>
+        <v>99367429</v>
       </c>
       <c r="B2" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>100045</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FM-120-3-33, Upl</t>
+          <t>FM-51-5-72, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>674813.8044771561</v>
+        <v>674818</v>
       </c>
       <c r="R2" t="n">
-        <v>6697122.325832795</v>
+        <v>6697244</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>05:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99308320</v>
+        <v>99365809</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>102976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,14 +825,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FM-120-3-33, Upl</t>
+          <t>FM-724-4-21, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674813.8044771561</v>
+        <v>674817</v>
       </c>
       <c r="R3" t="n">
-        <v>6697122.325832795</v>
+        <v>6697326</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-05-31</t>
+          <t>2002-06-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-05-31</t>
+          <t>2002-06-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,42 +905,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99329029</v>
+        <v>99329031</v>
       </c>
       <c r="B4" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>102987</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>674821.3868791274</v>
+        <v>674822</v>
       </c>
       <c r="R4" t="n">
-        <v>6697088.51113649</v>
+        <v>6697088</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1035,15 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99371046</v>
+        <v>99329026</v>
       </c>
       <c r="B5" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,38 +1031,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>FM-9740-4-42, Upl</t>
+          <t>FM-19915-5-69, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>674805.0130022146</v>
+        <v>674822</v>
       </c>
       <c r="R5" t="n">
-        <v>6697119.425722905</v>
+        <v>6697088</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,22 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2002-06-04</t>
+          <t>2013-05-31</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2002-06-04</t>
+          <t>2013-05-31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,15 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99371050</v>
+        <v>99371228</v>
       </c>
       <c r="B6" t="n">
-        <v>57068</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,16 +1146,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103057</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1195,14 +1170,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>FM-9740-4-42, Upl</t>
+          <t>FM-9647-5-10, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>674805.0130022146</v>
+        <v>674830</v>
       </c>
       <c r="R6" t="n">
-        <v>6697119.425722905</v>
+        <v>6697159</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1229,22 +1204,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2002-06-04</t>
+          <t>2003-05-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2002-06-04</t>
+          <t>2003-05-05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,32 +1250,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99365809</v>
+        <v>99320506</v>
       </c>
       <c r="B7" t="n">
-        <v>55667</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102976</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1315,14 +1285,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>FM-724-4-21, Upl</t>
+          <t>FM-1607-2-83, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>674816.374976885</v>
+        <v>674837</v>
       </c>
       <c r="R7" t="n">
-        <v>6697326.531143205</v>
+        <v>6697343</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1349,22 +1319,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2002-06-13</t>
+          <t>2003-05-15</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2002-06-13</t>
+          <t>2003-05-15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>05:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,32 +1365,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99367422</v>
+        <v>99367423</v>
       </c>
       <c r="B8" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103042</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1430,7 +1395,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1439,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>674817.3554921232</v>
+        <v>674818</v>
       </c>
       <c r="R8" t="n">
-        <v>6697244.352702629</v>
+        <v>6697244</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1515,54 +1480,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99371051</v>
+        <v>99371212</v>
       </c>
       <c r="B9" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>FM-9740-4-42, Upl</t>
+          <t>FM-9651-4-35, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>674805.0130022146</v>
+        <v>674824</v>
       </c>
       <c r="R9" t="n">
-        <v>6697119.425722905</v>
+        <v>6697270</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1589,22 +1549,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2002-06-04</t>
+          <t>2003-05-05</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2002-06-04</t>
+          <t>2003-05-05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,6 +1588,1271 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>99308319</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>FM-120-3-33, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>674814</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6697122</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>99371046</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>FM-9740-4-42, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>674805</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6697119</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>99371051</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>FM-9740-4-42, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>674805</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6697119</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>99329029</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>FM-19915-5-69, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>674822</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6697088</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2007-06-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2007-06-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>99367422</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>FM-51-5-72, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>674818</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6697244</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2018-06-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>99320508</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>FM-1607-2-83, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>674837</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6697343</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2003-05-15</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>05:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2003-05-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>05:08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>99343035</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>FM-3281-4-62, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>674835</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6697326</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2007-05-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2007-05-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>05:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>99365806</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>FM-724-4-21, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>674817</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6697326</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2002-06-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2002-06-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>99308320</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>FM-120-3-33, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>674814</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6697122</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2013-05-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2013-05-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>06:58</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>99371050</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>FM-9740-4-42, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>674805</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6697119</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>99371148</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58649</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103057</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sävsparv</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Emberiza schoeniclus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>FM-9678-4-10, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>674828</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6697088</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2002-06-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
         <is>
           <t>Forsmark platsundersökning</t>
         </is>

--- a/artfynd/A 23496-2023 artfynd.xlsx
+++ b/artfynd/A 23496-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367429</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99365809</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329031</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99371228</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1362,6 +1392,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99320506</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1477,6 +1512,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367423</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99371212</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,6 +1752,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99308319</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99371046</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1937,6 +1992,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99371051</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2052,6 +2112,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329029</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2167,6 +2232,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99367422</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2282,6 +2352,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99320508</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2397,6 +2472,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99343035</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2512,6 +2592,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99365806</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2627,6 +2712,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99308320</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2742,6 +2832,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99371050</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2857,8 +2952,34 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99371148</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>